--- a/click_order_data/result/analysis_summary_report.xlsx
+++ b/click_order_data/result/analysis_summary_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Video Performance List_20251209031458.xlsx</t>
+          <t>Video Performance List_20251209083422.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,31 +497,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="I2" t="n">
-        <v>294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>3337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Video Performance List_20251209031458.xlsx</t>
+          <t>Video Performance List_20251209083422.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -535,31 +529,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04444444444444445</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1749666666666667</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.07101666666666667</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5992</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>55474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Video Performance List_20251209031458.xlsx</t>
+          <t>Video Performance List_20251209083422.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -573,31 +561,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09316770186335403</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1438866666666666</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.07001333333333333</v>
-      </c>
-      <c r="I4" t="n">
-        <v>298.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>11039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Video Performance List_20251209031458.xlsx</t>
+          <t>Video Performance List_20251209083422.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -629,7 +611,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Video Performance List_20251209031458.xlsx</t>
+          <t>Video Performance List_20251209083422.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -656,6 +638,76 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Video Performance List_20251209083422.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[Date Range]: 2025-12-01 ~ 2025-12-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>车载手机支架</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5960.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27301</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Video Performance List_20251209083422.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[Date Range]: 2025-12-01 ~ 2025-12-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>电动修眉刀</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1373</v>
       </c>
     </row>
   </sheetData>
